--- a/web/files/九龙-九龙塘-皇廷汇.xlsx
+++ b/web/files/九龙-九龙塘-皇廷汇.xlsx
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>10718</v>
+        <v>10945</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -757,7 +757,7 @@
         <v>340000000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>31722</v>
+        <v>31064</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5845</v>
+        <v>7083</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>254800000</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>43593</v>
+        <v>35973</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -989,19 +989,19 @@
       <c r="B6" s="16" t="inlineStr">
         <is>
           <t>A号屋
-10718呎 (4+房)
+10945呎 (4+房)
 (24年-03月-21日)
 $3.40亿
-$31,722/呎</t>
+$31,064/呎</t>
         </is>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
           <t>B号屋
-5845呎 (4+房)
+7083呎 (4+房)
 (23年-08月-17日)
 $2.55亿
-$43,593/呎</t>
+$35,973/呎</t>
         </is>
       </c>
       <c r="D6" s="17" t="inlineStr">
